--- a/SQL/Normalizacion/Normalizacion-ejercicio-2-version2.xlsx
+++ b/SQL/Normalizacion/Normalizacion-ejercicio-2-version2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MarcoLopez\Downloads\Repos\DUAD\DUAD\SQL\Normalizacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92C6CC03-9A7E-4BCE-A615-BCE3912CD4AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55EA847-0AC2-48B7-9F5C-08E8E01EC822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C9327F3C-E3E9-4126-ABC7-3E65DBC78621}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="53">
   <si>
     <t>VIN</t>
   </si>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t>Company_ID</t>
+  </si>
+  <si>
+    <t>Model_ID</t>
   </si>
 </sst>
 </file>
@@ -820,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>3</v>
@@ -834,8 +837,8 @@
       <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>12</v>
+      <c r="C10" s="2">
+        <v>1</v>
       </c>
       <c r="D10" s="2">
         <v>2003</v>
@@ -849,8 +852,8 @@
       <c r="B11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>23</v>
+      <c r="C11" s="2">
+        <v>2</v>
       </c>
       <c r="D11" s="2">
         <v>2014</v>
@@ -864,8 +867,8 @@
       <c r="B12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>31</v>
+      <c r="C12" s="2">
+        <v>3</v>
       </c>
       <c r="D12" s="2">
         <v>2015</v>
@@ -1003,7 +1006,7 @@
         <v>47</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>1</v>
@@ -1053,12 +1056,9 @@
         <v>48</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D32" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1067,10 +1067,7 @@
       <c r="B33" s="2">
         <v>1</v>
       </c>
-      <c r="C33" s="2">
-        <v>1</v>
-      </c>
-      <c r="D33" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1079,10 +1076,7 @@
       <c r="B34" s="2">
         <v>2</v>
       </c>
-      <c r="C34" s="2">
-        <v>2</v>
-      </c>
-      <c r="D34" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1091,10 +1085,7 @@
       <c r="B35" s="2">
         <v>3</v>
       </c>
-      <c r="C35" s="2">
-        <v>3</v>
-      </c>
-      <c r="D35" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1103,10 +1094,7 @@
       <c r="B36" s="2">
         <v>4</v>
       </c>
-      <c r="C36" s="2">
-        <v>4</v>
-      </c>
-      <c r="D36" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1118,7 +1106,7 @@
         <v>50</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>41</v>
@@ -1129,8 +1117,8 @@
       <c r="B39" s="2">
         <v>1</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>16</v>
+      <c r="C39" s="2">
+        <v>1</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>17</v>
@@ -1141,8 +1129,8 @@
       <c r="B40" s="2">
         <v>2</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>20</v>
+      <c r="C40" s="2">
+        <v>2</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>21</v>
@@ -1153,8 +1141,8 @@
       <c r="B41" s="2">
         <v>3</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>27</v>
+      <c r="C41" s="2">
+        <v>3</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>28</v>
@@ -1165,8 +1153,8 @@
       <c r="B42" s="2">
         <v>4</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>35</v>
+      <c r="C42" s="2">
+        <v>4</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>36</v>
@@ -1236,14 +1224,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A26:A29"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="A20:A24"/>
     <mergeCell ref="A32:A36"/>
     <mergeCell ref="A38:A42"/>
     <mergeCell ref="A44:A48"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A26:A29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
